--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="R86796329633b4b4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="R8b1b30dffbdf4c19"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="R8b1b30dffbdf4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="Rfe56ef597f2d4014"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="Rfe56ef597f2d4014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="R843e1e07fa674373"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261013" sheetId="1" r:id="R843e1e07fa674373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261014" sheetId="1" r:id="R429ddbdc9415466c"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
-  <x:si>
-    <x:t>Daily Holdings (%)  10/13/2026</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="174">
+  <x:si>
+    <x:t>Daily Holdings (%)  10/14/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>62,977,808</x:t>
+    <x:t>62,513,858</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,391,688,684.16</x:t>
+    <x:t>$13,834,316,775.40</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>20.04%</x:t>
+    <x:t>20.20%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,13 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>15,048,413</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,698,349,594.56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.33%</x:t>
+    <x:t>14,937,551</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,423,146,930.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.38%</x:t>
   </x:si>
   <x:si>
     <x:t>AMD</x:t>
@@ -94,13 +94,13 @@
     <x:t>BBG000BBQCY0</x:t>
   </x:si>
   <x:si>
-    <x:t>6,758,004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$4,092,174,162.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.70%</x:t>
+    <x:t>6,708,216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,829,183,857.12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.59%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -112,13 +112,13 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>10,988,120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,926,165,157.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.47%</x:t>
+    <x:t>10,906,976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,776,540,440.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.52%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -130,13 +130,49 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>12,087,660</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,479,432,931.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.84%</x:t>
+    <x:t>11,998,398</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,367,350,398.70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Micron Technology Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000C5Z1S3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,401,192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,109,131,642.96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.54%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kla Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BMTFR4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,159,630</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,068,313,440.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.48%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -148,49 +184,31 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>12,564,605</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,376,423,478.63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.70%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Micron Technology Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000C5Z1S3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,426,428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,265,522,941.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.55%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kla Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BMTFR4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17,287,286</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,180,860,624.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.43%</x:t>
+    <x:t>12,472,049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,059,144,178.72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.47%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analog Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BB6G37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,526,156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,037,330,776.92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.44%</x:t>
   </x:si>
   <x:si>
     <x:t>ASML</x:t>
@@ -202,30 +220,15 @@
     <x:t>BBG000K6MRN4</x:t>
   </x:si>
   <x:si>
-    <x:t>1,832,529</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,147,845,015.04</x:t>
+    <x:t>1,819,029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,001,397,850.00</x:t>
   </x:si>
   <x:si>
     <x:t>4.38%</x:t>
   </x:si>
   <x:si>
-    <x:t>ADI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Analog Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BB6G37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,582,136</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,144,311,799.20</x:t>
-  </x:si>
-  <x:si>
     <x:t>AMAT</x:t>
   </x:si>
   <x:si>
@@ -235,13 +238,13 @@
     <x:t>BBG000BBPFB9</x:t>
   </x:si>
   <x:si>
-    <x:t>6,744,193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,130,924,158.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.36%</x:t>
+    <x:t>6,694,387</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,989,914,065.81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.37%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC</x:t>
@@ -253,13 +256,13 @@
     <x:t>BBG000C0G1D1</x:t>
   </x:si>
   <x:si>
-    <x:t>29,762,910</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,059,924,777.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.26%</x:t>
+    <x:t>29,543,130</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,898,771,915.60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.23%</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -271,13 +274,13 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>10,011,461</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,014,551,021.71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.20%</x:t>
+    <x:t>9,937,535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,851,277,542.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.16%</x:t>
   </x:si>
   <x:si>
     <x:t>SKHY</x:t>
@@ -289,13 +292,13 @@
     <x:t>BBG0238L5JS9</x:t>
   </x:si>
   <x:si>
-    <x:t>17,729,250</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,784,556,005.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.88%</x:t>
+    <x:t>17,598,642</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,596,679,627.10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.79%</x:t>
   </x:si>
   <x:si>
     <x:t>QCOM</x:t>
@@ -307,13 +310,13 @@
     <x:t>BBG000CGC1X8</x:t>
   </x:si>
   <x:si>
-    <x:t>15,009,755</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,654,625,269.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.70%</x:t>
+    <x:t>14,898,929</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,571,853,123.98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.76%</x:t>
   </x:si>
   <x:si>
     <x:t>SNPS</x:t>
@@ -325,13 +328,13 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,035,604</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,501,136,534.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.09%</x:t>
+    <x:t>3,013,194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,446,122,196.42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.11%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -343,13 +346,13 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,309,179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,440,127,621.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.01%</x:t>
+    <x:t>4,277,355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,409,217,378.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.06%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -361,13 +364,13 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,325,493</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$884,361,732.97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.23%</x:t>
+    <x:t>2,308,321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$829,702,900.24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.21%</x:t>
   </x:si>
   <x:si>
     <x:t>MPWR</x:t>
@@ -379,13 +382,13 @@
     <x:t>BBG000C30L48</x:t>
   </x:si>
   <x:si>
-    <x:t>655,036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$864,352,753.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.20%</x:t>
+    <x:t>650,194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$808,262,663.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.18%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB</x:t>
@@ -397,13 +400,31 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,345,898</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$763,378,668.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.06%</x:t>
+    <x:t>2,328,582</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$699,226,602.96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.02%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NXPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nxp Semiconductors Nv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BND699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,146,713</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$694,888,631.79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.01%</x:t>
   </x:si>
   <x:si>
     <x:t>ARM</x:t>
@@ -415,28 +436,10 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>2,888,363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$737,659,026.57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.03%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NXPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nxp Semiconductors Nv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BND699</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,170,113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$717,459,974.16</x:t>
+    <x:t>2,867,033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$682,382,524.33</x:t>
   </x:si>
   <x:si>
     <x:t>1.00%</x:t>
@@ -451,13 +454,13 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>12,674,708</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$628,285,275.56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.87%</x:t>
+    <x:t>12,581,108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$590,053,965.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.86%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -469,10 +472,10 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,447,655</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$552,318,094.80</x:t>
+    <x:t>7,392,665</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$526,727,381.25</x:t>
   </x:si>
   <x:si>
     <x:t>0.77%</x:t>
@@ -487,10 +490,10 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,587,534</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$351,817,982.46</x:t>
+    <x:t>4,553,658</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$334,056,350.88</x:t>
   </x:si>
   <x:si>
     <x:t>0.49%</x:t>
@@ -502,13 +505,13 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>42,568,818</x:t>
+    <x:t>43,883,894</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$42,568,817.82</x:t>
+    <x:t>$43,883,893.64</x:t>
   </x:si>
   <x:si>
     <x:t>0.06%</x:t>
@@ -520,7 +523,7 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-6,814,694.57</x:t>
+    <x:t>$-8,804,655.45</x:t>
   </x:si>
   <x:si>
     <x:t>-0.01%</x:t>
@@ -984,7 +987,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9" ht="15" customHeight="1">
@@ -992,28 +995,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9" ht="15" customHeight="1">
@@ -1021,28 +1024,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9" ht="15" customHeight="1">
@@ -1050,28 +1053,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9" ht="15" customHeight="1">
@@ -1079,28 +1082,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9" ht="15" customHeight="1">
@@ -1108,28 +1111,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I18" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15" customHeight="1">
@@ -1137,28 +1140,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15" customHeight="1">
@@ -1166,28 +1169,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9" ht="15" customHeight="1">
@@ -1195,28 +1198,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9" ht="15" customHeight="1">
@@ -1224,28 +1227,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15" customHeight="1">
@@ -1253,28 +1256,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I23" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15" customHeight="1">
@@ -1282,28 +1285,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I24" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15" customHeight="1">
@@ -1311,28 +1314,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I25" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15" customHeight="1">
@@ -1340,28 +1343,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I26" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9" ht="15" customHeight="1">
@@ -1369,28 +1372,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I27" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9" ht="15" customHeight="1">
@@ -1398,28 +1401,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I28" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9" ht="15" customHeight="1">
@@ -1427,28 +1430,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I29" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15" customHeight="1">
@@ -1459,7 +1462,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>17</x:v>
@@ -1468,21 +1471,21 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I30" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9" ht="15" customHeight="1">
       <x:c r="A31" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
         <x:v>1</x:v>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-15.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261014" sheetId="1" r:id="R429ddbdc9415466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261014" sheetId="1" r:id="R332c61ae6b064125"/>
   </x:sheets>
 </x:workbook>
 </file>
